--- a/experiment/ELAN_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/ELAN_bestx4/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.08</v>
+        <v>24.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5736</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.7</v>
+        <v>28.74</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8132</v>
+        <v>0.8139</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.59</v>
+        <v>26.62</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8139</v>
+        <v>0.8146</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.62</v>
+        <v>30.66</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8488</v>
+        <v>0.8495</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.24</v>
+        <v>26.25</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7099</v>
+        <v>0.7104</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.97</v>
+        <v>34.01</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8938</v>
+        <v>0.8943</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.34</v>
+        <v>26.36</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7512</v>
+        <v>0.7524999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.11</v>
+        <v>23.12</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5928</v>
+        <v>0.5936</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.5</v>
+        <v>27.53</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7887</v>
+        <v>0.7894</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.34</v>
+        <v>29.35</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8044</v>
+        <v>0.8048999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.8</v>
+        <v>24.87</v>
       </c>
       <c r="C12" t="n">
-        <v>0.742</v>
+        <v>0.7453</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.06</v>
+        <v>28.08</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7565</v>
+        <v>0.7577</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.05</v>
+        <v>30.06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8086</v>
+        <v>0.8091</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.47</v>
+        <v>29.49</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8327</v>
+        <v>0.8336</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.09</v>
+        <v>25.1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6807</v>
+        <v>0.6811</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.95</v>
+        <v>24.99</v>
       </c>
       <c r="C17" t="n">
-        <v>0.763</v>
+        <v>0.7642</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.79</v>
+        <v>34.83</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8939</v>
+        <v>0.8945</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.93</v>
+        <v>32.98</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8938</v>
+        <v>0.8945</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         <v>26.26</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7398</v>
+        <v>0.7407</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>26.1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8018</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.28</v>
+        <v>22.32</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6933</v>
+        <v>0.6971000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.99</v>
+        <v>24</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24.85</v>
+        <v>24.86</v>
       </c>
       <c r="C24" t="n">
-        <v>0.574</v>
+        <v>0.5743</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.62</v>
+        <v>26.66</v>
       </c>
       <c r="C25" t="n">
-        <v>0.793</v>
+        <v>0.7947</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.75</v>
+        <v>27.79</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8239</v>
+        <v>0.8248</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.03</v>
+        <v>27.05</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8387</v>
+        <v>0.8396</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.8</v>
+        <v>27.82</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7383</v>
+        <v>0.7396</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.6</v>
+        <v>29.63</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8026</v>
+        <v>0.8037</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.6</v>
+        <v>32.65</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9032</v>
+        <v>0.9033</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         <v>19.94</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5071</v>
+        <v>0.5078</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.82</v>
+        <v>29.84</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8186</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>20.97</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4324</v>
+        <v>0.4335</v>
       </c>
     </row>
     <row r="34">
@@ -871,7 +871,7 @@
         <v>25.26</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6755</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.56</v>
+        <v>24.59</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7603</v>
+        <v>0.7613</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.78</v>
+        <v>34.87</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8923</v>
+        <v>0.8928</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.03</v>
+        <v>27.07</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7428</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.93</v>
+        <v>27.94</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5143</v>
+        <v>0.5144</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.28</v>
+        <v>28.32</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7186</v>
+        <v>0.7196</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.53</v>
+        <v>28.56</v>
       </c>
       <c r="C40" t="n">
-        <v>0.747</v>
+        <v>0.7484</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.23</v>
+        <v>36.42</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9568</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         <v>26.96</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7482</v>
+        <v>0.7486</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.88</v>
+        <v>25.91</v>
       </c>
       <c r="C43" t="n">
-        <v>0.724</v>
+        <v>0.7256</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.83</v>
+        <v>26.84</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7623</v>
+        <v>0.7625999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.01</v>
+        <v>28.05</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8763</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.84</v>
+        <v>24.85</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6859</v>
+        <v>0.6871</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.76</v>
+        <v>34.8</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8735000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.82</v>
+        <v>22.86</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6267</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25.01</v>
+        <v>25.02</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6359</v>
+        <v>0.6372</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.39</v>
+        <v>27.43</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8769</v>
+        <v>0.8782</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.22</v>
+        <v>32.2</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8408</v>
+        <v>0.8407</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.87</v>
+        <v>24.9</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6226</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.74</v>
+        <v>22.78</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7077</v>
+        <v>0.7093</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.55</v>
+        <v>32.57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8464</v>
+        <v>0.8468</v>
       </c>
     </row>
     <row r="55">
@@ -1144,7 +1144,7 @@
         <v>32.58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8011</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.87</v>
+        <v>27.88</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7814</v>
+        <v>0.7823</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.68</v>
+        <v>25.72</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6984</v>
+        <v>0.7000999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.48</v>
+        <v>21.49</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4262</v>
+        <v>0.4275</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.5</v>
+        <v>27.51</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7288</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         <v>32.02</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7926</v>
+        <v>0.7927</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.3</v>
+        <v>31.32</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7867</v>
+        <v>0.7872</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.78</v>
+        <v>31.8</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8162</v>
+        <v>0.8168</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>29.03</v>
+        <v>29.06</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7952</v>
+        <v>0.7955</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.86</v>
+        <v>33.98</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9526</v>
+        <v>0.9532</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.35</v>
+        <v>24.37</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6734</v>
+        <v>0.6746</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26.07</v>
+        <v>26.08</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6227</v>
+        <v>0.6233</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.35</v>
+        <v>28.38</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7942</v>
+        <v>0.7952</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>40.08</v>
+        <v>40.14</v>
       </c>
       <c r="C68" t="n">
-        <v>0.981</v>
+        <v>0.9812</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.12</v>
+        <v>21.13</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5829</v>
+        <v>0.5832000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.81</v>
+        <v>22.83</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6518</v>
+        <v>0.6526999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28.98</v>
+        <v>29.02</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8115</v>
+        <v>0.8127</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.62</v>
+        <v>30.66</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8207</v>
+        <v>0.822</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.47</v>
+        <v>25.49</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5974</v>
+        <v>0.5982</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>27.22</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.6066</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.32</v>
+        <v>26.33</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6978</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.2</v>
+        <v>24.21</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6997</v>
+        <v>0.7008</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         <v>30.69</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7855</v>
+        <v>0.7856</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23.66</v>
+        <v>23.67</v>
       </c>
       <c r="C78" t="n">
-        <v>0.478</v>
+        <v>0.4782</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>29.87</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8119</v>
+        <v>0.8118</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.91</v>
+        <v>32.92</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9526</v>
+        <v>0.9529</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>29.78</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8193</v>
+        <v>0.8195</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.78</v>
+        <v>35.83</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9389</v>
+        <v>0.9393</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.54</v>
+        <v>28.56</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7194</v>
+        <v>0.7202</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.28</v>
+        <v>22.29</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5324</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.11</v>
+        <v>21.12</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6076</v>
+        <v>0.6093</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.72</v>
+        <v>25.74</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7911</v>
+        <v>0.7926</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.05</v>
+        <v>25.06</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6047</v>
+        <v>0.6057</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.39</v>
+        <v>27.41</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6956</v>
+        <v>0.6968</v>
       </c>
     </row>
     <row r="89">
@@ -1586,7 +1586,7 @@
         <v>30.75</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8145</v>
+        <v>0.8148</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>27.23</v>
+        <v>27.25</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5614</v>
+        <v>0.5621</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.16</v>
+        <v>25.19</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6505</v>
+        <v>0.6521</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.06</v>
+        <v>29.1</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7145</v>
+        <v>0.7154</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.84</v>
+        <v>26.94</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7604</v>
+        <v>0.7633</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.94</v>
+        <v>30.95</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8799</v>
+        <v>0.8801</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26.06</v>
+        <v>26.09</v>
       </c>
       <c r="C95" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.49</v>
+        <v>26.53</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8109</v>
+        <v>0.8133</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         <v>21.94</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3186</v>
+        <v>0.3185</v>
       </c>
     </row>
     <row r="98">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>27.04</v>
+        <v>27.05</v>
       </c>
       <c r="C98" t="n">
         <v>0.5635</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.36</v>
+        <v>26.38</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7803</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.95</v>
+        <v>26.97</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7366</v>
+        <v>0.7374000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.24</v>
+        <v>25.27</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7315</v>
+        <v>0.7337</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.61</v>
+        <v>27.64</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7379</v>
+        <v>0.7388</v>
       </c>
     </row>
   </sheetData>
